--- a/Stock material/Template_Stock.Inventory (2).xlsx
+++ b/Stock material/Template_Stock.Inventory (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UTC2\DoAnTotNghiep\Stock material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B3A185-242B-4ACD-96FC-7C394234D747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685DC405-EB20-4ECD-A836-0BB8992F6CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>No</t>
   </si>
@@ -198,21 +198,38 @@
     <t>OLD-MODEL-X1</t>
   </si>
   <si>
-    <t xml:space="preserve">
-FAKE-CR-01</t>
-  </si>
-  <si>
     <t>CR-Y120</t>
   </si>
   <si>
     <t>HCM Office</t>
+  </si>
+  <si>
+    <t>FAKE-SC-E1-01</t>
+  </si>
+  <si>
+    <t>SC-E1-4-0.4K</t>
+  </si>
+  <si>
+    <t>FAKE-MR-J4-01</t>
+  </si>
+  <si>
+    <t>MR-J4-10A</t>
+  </si>
+  <si>
+    <t>FR-E840-0.75K</t>
+  </si>
+  <si>
+    <t>FAKE-CR-01</t>
+  </si>
+  <si>
+    <t>FAKE-FR-E840-02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -275,12 +292,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF325168"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -381,7 +392,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -399,7 +410,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -430,15 +440,163 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -819,327 +977,327 @@
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="6.44140625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="113" style="9" customWidth="1"/>
-    <col min="3" max="251" width="8.88671875" style="8"/>
-    <col min="252" max="252" width="6.44140625" style="8" customWidth="1"/>
-    <col min="253" max="253" width="113" style="8" customWidth="1"/>
-    <col min="254" max="507" width="8.88671875" style="8"/>
-    <col min="508" max="508" width="6.44140625" style="8" customWidth="1"/>
-    <col min="509" max="509" width="113" style="8" customWidth="1"/>
-    <col min="510" max="763" width="8.88671875" style="8"/>
-    <col min="764" max="764" width="6.44140625" style="8" customWidth="1"/>
-    <col min="765" max="765" width="113" style="8" customWidth="1"/>
-    <col min="766" max="1019" width="8.88671875" style="8"/>
-    <col min="1020" max="1020" width="6.44140625" style="8" customWidth="1"/>
-    <col min="1021" max="1021" width="113" style="8" customWidth="1"/>
-    <col min="1022" max="1275" width="8.88671875" style="8"/>
-    <col min="1276" max="1276" width="6.44140625" style="8" customWidth="1"/>
-    <col min="1277" max="1277" width="113" style="8" customWidth="1"/>
-    <col min="1278" max="1531" width="8.88671875" style="8"/>
-    <col min="1532" max="1532" width="6.44140625" style="8" customWidth="1"/>
-    <col min="1533" max="1533" width="113" style="8" customWidth="1"/>
-    <col min="1534" max="1787" width="8.88671875" style="8"/>
-    <col min="1788" max="1788" width="6.44140625" style="8" customWidth="1"/>
-    <col min="1789" max="1789" width="113" style="8" customWidth="1"/>
-    <col min="1790" max="2043" width="8.88671875" style="8"/>
-    <col min="2044" max="2044" width="6.44140625" style="8" customWidth="1"/>
-    <col min="2045" max="2045" width="113" style="8" customWidth="1"/>
-    <col min="2046" max="2299" width="8.88671875" style="8"/>
-    <col min="2300" max="2300" width="6.44140625" style="8" customWidth="1"/>
-    <col min="2301" max="2301" width="113" style="8" customWidth="1"/>
-    <col min="2302" max="2555" width="8.88671875" style="8"/>
-    <col min="2556" max="2556" width="6.44140625" style="8" customWidth="1"/>
-    <col min="2557" max="2557" width="113" style="8" customWidth="1"/>
-    <col min="2558" max="2811" width="8.88671875" style="8"/>
-    <col min="2812" max="2812" width="6.44140625" style="8" customWidth="1"/>
-    <col min="2813" max="2813" width="113" style="8" customWidth="1"/>
-    <col min="2814" max="3067" width="8.88671875" style="8"/>
-    <col min="3068" max="3068" width="6.44140625" style="8" customWidth="1"/>
-    <col min="3069" max="3069" width="113" style="8" customWidth="1"/>
-    <col min="3070" max="3323" width="8.88671875" style="8"/>
-    <col min="3324" max="3324" width="6.44140625" style="8" customWidth="1"/>
-    <col min="3325" max="3325" width="113" style="8" customWidth="1"/>
-    <col min="3326" max="3579" width="8.88671875" style="8"/>
-    <col min="3580" max="3580" width="6.44140625" style="8" customWidth="1"/>
-    <col min="3581" max="3581" width="113" style="8" customWidth="1"/>
-    <col min="3582" max="3835" width="8.88671875" style="8"/>
-    <col min="3836" max="3836" width="6.44140625" style="8" customWidth="1"/>
-    <col min="3837" max="3837" width="113" style="8" customWidth="1"/>
-    <col min="3838" max="4091" width="8.88671875" style="8"/>
-    <col min="4092" max="4092" width="6.44140625" style="8" customWidth="1"/>
-    <col min="4093" max="4093" width="113" style="8" customWidth="1"/>
-    <col min="4094" max="4347" width="8.88671875" style="8"/>
-    <col min="4348" max="4348" width="6.44140625" style="8" customWidth="1"/>
-    <col min="4349" max="4349" width="113" style="8" customWidth="1"/>
-    <col min="4350" max="4603" width="8.88671875" style="8"/>
-    <col min="4604" max="4604" width="6.44140625" style="8" customWidth="1"/>
-    <col min="4605" max="4605" width="113" style="8" customWidth="1"/>
-    <col min="4606" max="4859" width="8.88671875" style="8"/>
-    <col min="4860" max="4860" width="6.44140625" style="8" customWidth="1"/>
-    <col min="4861" max="4861" width="113" style="8" customWidth="1"/>
-    <col min="4862" max="5115" width="8.88671875" style="8"/>
-    <col min="5116" max="5116" width="6.44140625" style="8" customWidth="1"/>
-    <col min="5117" max="5117" width="113" style="8" customWidth="1"/>
-    <col min="5118" max="5371" width="8.88671875" style="8"/>
-    <col min="5372" max="5372" width="6.44140625" style="8" customWidth="1"/>
-    <col min="5373" max="5373" width="113" style="8" customWidth="1"/>
-    <col min="5374" max="5627" width="8.88671875" style="8"/>
-    <col min="5628" max="5628" width="6.44140625" style="8" customWidth="1"/>
-    <col min="5629" max="5629" width="113" style="8" customWidth="1"/>
-    <col min="5630" max="5883" width="8.88671875" style="8"/>
-    <col min="5884" max="5884" width="6.44140625" style="8" customWidth="1"/>
-    <col min="5885" max="5885" width="113" style="8" customWidth="1"/>
-    <col min="5886" max="6139" width="8.88671875" style="8"/>
-    <col min="6140" max="6140" width="6.44140625" style="8" customWidth="1"/>
-    <col min="6141" max="6141" width="113" style="8" customWidth="1"/>
-    <col min="6142" max="6395" width="8.88671875" style="8"/>
-    <col min="6396" max="6396" width="6.44140625" style="8" customWidth="1"/>
-    <col min="6397" max="6397" width="113" style="8" customWidth="1"/>
-    <col min="6398" max="6651" width="8.88671875" style="8"/>
-    <col min="6652" max="6652" width="6.44140625" style="8" customWidth="1"/>
-    <col min="6653" max="6653" width="113" style="8" customWidth="1"/>
-    <col min="6654" max="6907" width="8.88671875" style="8"/>
-    <col min="6908" max="6908" width="6.44140625" style="8" customWidth="1"/>
-    <col min="6909" max="6909" width="113" style="8" customWidth="1"/>
-    <col min="6910" max="7163" width="8.88671875" style="8"/>
-    <col min="7164" max="7164" width="6.44140625" style="8" customWidth="1"/>
-    <col min="7165" max="7165" width="113" style="8" customWidth="1"/>
-    <col min="7166" max="7419" width="8.88671875" style="8"/>
-    <col min="7420" max="7420" width="6.44140625" style="8" customWidth="1"/>
-    <col min="7421" max="7421" width="113" style="8" customWidth="1"/>
-    <col min="7422" max="7675" width="8.88671875" style="8"/>
-    <col min="7676" max="7676" width="6.44140625" style="8" customWidth="1"/>
-    <col min="7677" max="7677" width="113" style="8" customWidth="1"/>
-    <col min="7678" max="7931" width="8.88671875" style="8"/>
-    <col min="7932" max="7932" width="6.44140625" style="8" customWidth="1"/>
-    <col min="7933" max="7933" width="113" style="8" customWidth="1"/>
-    <col min="7934" max="8187" width="8.88671875" style="8"/>
-    <col min="8188" max="8188" width="6.44140625" style="8" customWidth="1"/>
-    <col min="8189" max="8189" width="113" style="8" customWidth="1"/>
-    <col min="8190" max="8443" width="8.88671875" style="8"/>
-    <col min="8444" max="8444" width="6.44140625" style="8" customWidth="1"/>
-    <col min="8445" max="8445" width="113" style="8" customWidth="1"/>
-    <col min="8446" max="8699" width="8.88671875" style="8"/>
-    <col min="8700" max="8700" width="6.44140625" style="8" customWidth="1"/>
-    <col min="8701" max="8701" width="113" style="8" customWidth="1"/>
-    <col min="8702" max="8955" width="8.88671875" style="8"/>
-    <col min="8956" max="8956" width="6.44140625" style="8" customWidth="1"/>
-    <col min="8957" max="8957" width="113" style="8" customWidth="1"/>
-    <col min="8958" max="9211" width="8.88671875" style="8"/>
-    <col min="9212" max="9212" width="6.44140625" style="8" customWidth="1"/>
-    <col min="9213" max="9213" width="113" style="8" customWidth="1"/>
-    <col min="9214" max="9467" width="8.88671875" style="8"/>
-    <col min="9468" max="9468" width="6.44140625" style="8" customWidth="1"/>
-    <col min="9469" max="9469" width="113" style="8" customWidth="1"/>
-    <col min="9470" max="9723" width="8.88671875" style="8"/>
-    <col min="9724" max="9724" width="6.44140625" style="8" customWidth="1"/>
-    <col min="9725" max="9725" width="113" style="8" customWidth="1"/>
-    <col min="9726" max="9979" width="8.88671875" style="8"/>
-    <col min="9980" max="9980" width="6.44140625" style="8" customWidth="1"/>
-    <col min="9981" max="9981" width="113" style="8" customWidth="1"/>
-    <col min="9982" max="10235" width="8.88671875" style="8"/>
-    <col min="10236" max="10236" width="6.44140625" style="8" customWidth="1"/>
-    <col min="10237" max="10237" width="113" style="8" customWidth="1"/>
-    <col min="10238" max="10491" width="8.88671875" style="8"/>
-    <col min="10492" max="10492" width="6.44140625" style="8" customWidth="1"/>
-    <col min="10493" max="10493" width="113" style="8" customWidth="1"/>
-    <col min="10494" max="10747" width="8.88671875" style="8"/>
-    <col min="10748" max="10748" width="6.44140625" style="8" customWidth="1"/>
-    <col min="10749" max="10749" width="113" style="8" customWidth="1"/>
-    <col min="10750" max="11003" width="8.88671875" style="8"/>
-    <col min="11004" max="11004" width="6.44140625" style="8" customWidth="1"/>
-    <col min="11005" max="11005" width="113" style="8" customWidth="1"/>
-    <col min="11006" max="11259" width="8.88671875" style="8"/>
-    <col min="11260" max="11260" width="6.44140625" style="8" customWidth="1"/>
-    <col min="11261" max="11261" width="113" style="8" customWidth="1"/>
-    <col min="11262" max="11515" width="8.88671875" style="8"/>
-    <col min="11516" max="11516" width="6.44140625" style="8" customWidth="1"/>
-    <col min="11517" max="11517" width="113" style="8" customWidth="1"/>
-    <col min="11518" max="11771" width="8.88671875" style="8"/>
-    <col min="11772" max="11772" width="6.44140625" style="8" customWidth="1"/>
-    <col min="11773" max="11773" width="113" style="8" customWidth="1"/>
-    <col min="11774" max="12027" width="8.88671875" style="8"/>
-    <col min="12028" max="12028" width="6.44140625" style="8" customWidth="1"/>
-    <col min="12029" max="12029" width="113" style="8" customWidth="1"/>
-    <col min="12030" max="12283" width="8.88671875" style="8"/>
-    <col min="12284" max="12284" width="6.44140625" style="8" customWidth="1"/>
-    <col min="12285" max="12285" width="113" style="8" customWidth="1"/>
-    <col min="12286" max="12539" width="8.88671875" style="8"/>
-    <col min="12540" max="12540" width="6.44140625" style="8" customWidth="1"/>
-    <col min="12541" max="12541" width="113" style="8" customWidth="1"/>
-    <col min="12542" max="12795" width="8.88671875" style="8"/>
-    <col min="12796" max="12796" width="6.44140625" style="8" customWidth="1"/>
-    <col min="12797" max="12797" width="113" style="8" customWidth="1"/>
-    <col min="12798" max="13051" width="8.88671875" style="8"/>
-    <col min="13052" max="13052" width="6.44140625" style="8" customWidth="1"/>
-    <col min="13053" max="13053" width="113" style="8" customWidth="1"/>
-    <col min="13054" max="13307" width="8.88671875" style="8"/>
-    <col min="13308" max="13308" width="6.44140625" style="8" customWidth="1"/>
-    <col min="13309" max="13309" width="113" style="8" customWidth="1"/>
-    <col min="13310" max="13563" width="8.88671875" style="8"/>
-    <col min="13564" max="13564" width="6.44140625" style="8" customWidth="1"/>
-    <col min="13565" max="13565" width="113" style="8" customWidth="1"/>
-    <col min="13566" max="13819" width="8.88671875" style="8"/>
-    <col min="13820" max="13820" width="6.44140625" style="8" customWidth="1"/>
-    <col min="13821" max="13821" width="113" style="8" customWidth="1"/>
-    <col min="13822" max="14075" width="8.88671875" style="8"/>
-    <col min="14076" max="14076" width="6.44140625" style="8" customWidth="1"/>
-    <col min="14077" max="14077" width="113" style="8" customWidth="1"/>
-    <col min="14078" max="14331" width="8.88671875" style="8"/>
-    <col min="14332" max="14332" width="6.44140625" style="8" customWidth="1"/>
-    <col min="14333" max="14333" width="113" style="8" customWidth="1"/>
-    <col min="14334" max="14587" width="8.88671875" style="8"/>
-    <col min="14588" max="14588" width="6.44140625" style="8" customWidth="1"/>
-    <col min="14589" max="14589" width="113" style="8" customWidth="1"/>
-    <col min="14590" max="14843" width="8.88671875" style="8"/>
-    <col min="14844" max="14844" width="6.44140625" style="8" customWidth="1"/>
-    <col min="14845" max="14845" width="113" style="8" customWidth="1"/>
-    <col min="14846" max="15099" width="8.88671875" style="8"/>
-    <col min="15100" max="15100" width="6.44140625" style="8" customWidth="1"/>
-    <col min="15101" max="15101" width="113" style="8" customWidth="1"/>
-    <col min="15102" max="15355" width="8.88671875" style="8"/>
-    <col min="15356" max="15356" width="6.44140625" style="8" customWidth="1"/>
-    <col min="15357" max="15357" width="113" style="8" customWidth="1"/>
-    <col min="15358" max="15611" width="8.88671875" style="8"/>
-    <col min="15612" max="15612" width="6.44140625" style="8" customWidth="1"/>
-    <col min="15613" max="15613" width="113" style="8" customWidth="1"/>
-    <col min="15614" max="15867" width="8.88671875" style="8"/>
-    <col min="15868" max="15868" width="6.44140625" style="8" customWidth="1"/>
-    <col min="15869" max="15869" width="113" style="8" customWidth="1"/>
-    <col min="15870" max="16123" width="8.88671875" style="8"/>
-    <col min="16124" max="16124" width="6.44140625" style="8" customWidth="1"/>
-    <col min="16125" max="16125" width="113" style="8" customWidth="1"/>
-    <col min="16126" max="16384" width="8.88671875" style="8"/>
+    <col min="1" max="1" width="6.44140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="113" style="8" customWidth="1"/>
+    <col min="3" max="251" width="8.88671875" style="7"/>
+    <col min="252" max="252" width="6.44140625" style="7" customWidth="1"/>
+    <col min="253" max="253" width="113" style="7" customWidth="1"/>
+    <col min="254" max="507" width="8.88671875" style="7"/>
+    <col min="508" max="508" width="6.44140625" style="7" customWidth="1"/>
+    <col min="509" max="509" width="113" style="7" customWidth="1"/>
+    <col min="510" max="763" width="8.88671875" style="7"/>
+    <col min="764" max="764" width="6.44140625" style="7" customWidth="1"/>
+    <col min="765" max="765" width="113" style="7" customWidth="1"/>
+    <col min="766" max="1019" width="8.88671875" style="7"/>
+    <col min="1020" max="1020" width="6.44140625" style="7" customWidth="1"/>
+    <col min="1021" max="1021" width="113" style="7" customWidth="1"/>
+    <col min="1022" max="1275" width="8.88671875" style="7"/>
+    <col min="1276" max="1276" width="6.44140625" style="7" customWidth="1"/>
+    <col min="1277" max="1277" width="113" style="7" customWidth="1"/>
+    <col min="1278" max="1531" width="8.88671875" style="7"/>
+    <col min="1532" max="1532" width="6.44140625" style="7" customWidth="1"/>
+    <col min="1533" max="1533" width="113" style="7" customWidth="1"/>
+    <col min="1534" max="1787" width="8.88671875" style="7"/>
+    <col min="1788" max="1788" width="6.44140625" style="7" customWidth="1"/>
+    <col min="1789" max="1789" width="113" style="7" customWidth="1"/>
+    <col min="1790" max="2043" width="8.88671875" style="7"/>
+    <col min="2044" max="2044" width="6.44140625" style="7" customWidth="1"/>
+    <col min="2045" max="2045" width="113" style="7" customWidth="1"/>
+    <col min="2046" max="2299" width="8.88671875" style="7"/>
+    <col min="2300" max="2300" width="6.44140625" style="7" customWidth="1"/>
+    <col min="2301" max="2301" width="113" style="7" customWidth="1"/>
+    <col min="2302" max="2555" width="8.88671875" style="7"/>
+    <col min="2556" max="2556" width="6.44140625" style="7" customWidth="1"/>
+    <col min="2557" max="2557" width="113" style="7" customWidth="1"/>
+    <col min="2558" max="2811" width="8.88671875" style="7"/>
+    <col min="2812" max="2812" width="6.44140625" style="7" customWidth="1"/>
+    <col min="2813" max="2813" width="113" style="7" customWidth="1"/>
+    <col min="2814" max="3067" width="8.88671875" style="7"/>
+    <col min="3068" max="3068" width="6.44140625" style="7" customWidth="1"/>
+    <col min="3069" max="3069" width="113" style="7" customWidth="1"/>
+    <col min="3070" max="3323" width="8.88671875" style="7"/>
+    <col min="3324" max="3324" width="6.44140625" style="7" customWidth="1"/>
+    <col min="3325" max="3325" width="113" style="7" customWidth="1"/>
+    <col min="3326" max="3579" width="8.88671875" style="7"/>
+    <col min="3580" max="3580" width="6.44140625" style="7" customWidth="1"/>
+    <col min="3581" max="3581" width="113" style="7" customWidth="1"/>
+    <col min="3582" max="3835" width="8.88671875" style="7"/>
+    <col min="3836" max="3836" width="6.44140625" style="7" customWidth="1"/>
+    <col min="3837" max="3837" width="113" style="7" customWidth="1"/>
+    <col min="3838" max="4091" width="8.88671875" style="7"/>
+    <col min="4092" max="4092" width="6.44140625" style="7" customWidth="1"/>
+    <col min="4093" max="4093" width="113" style="7" customWidth="1"/>
+    <col min="4094" max="4347" width="8.88671875" style="7"/>
+    <col min="4348" max="4348" width="6.44140625" style="7" customWidth="1"/>
+    <col min="4349" max="4349" width="113" style="7" customWidth="1"/>
+    <col min="4350" max="4603" width="8.88671875" style="7"/>
+    <col min="4604" max="4604" width="6.44140625" style="7" customWidth="1"/>
+    <col min="4605" max="4605" width="113" style="7" customWidth="1"/>
+    <col min="4606" max="4859" width="8.88671875" style="7"/>
+    <col min="4860" max="4860" width="6.44140625" style="7" customWidth="1"/>
+    <col min="4861" max="4861" width="113" style="7" customWidth="1"/>
+    <col min="4862" max="5115" width="8.88671875" style="7"/>
+    <col min="5116" max="5116" width="6.44140625" style="7" customWidth="1"/>
+    <col min="5117" max="5117" width="113" style="7" customWidth="1"/>
+    <col min="5118" max="5371" width="8.88671875" style="7"/>
+    <col min="5372" max="5372" width="6.44140625" style="7" customWidth="1"/>
+    <col min="5373" max="5373" width="113" style="7" customWidth="1"/>
+    <col min="5374" max="5627" width="8.88671875" style="7"/>
+    <col min="5628" max="5628" width="6.44140625" style="7" customWidth="1"/>
+    <col min="5629" max="5629" width="113" style="7" customWidth="1"/>
+    <col min="5630" max="5883" width="8.88671875" style="7"/>
+    <col min="5884" max="5884" width="6.44140625" style="7" customWidth="1"/>
+    <col min="5885" max="5885" width="113" style="7" customWidth="1"/>
+    <col min="5886" max="6139" width="8.88671875" style="7"/>
+    <col min="6140" max="6140" width="6.44140625" style="7" customWidth="1"/>
+    <col min="6141" max="6141" width="113" style="7" customWidth="1"/>
+    <col min="6142" max="6395" width="8.88671875" style="7"/>
+    <col min="6396" max="6396" width="6.44140625" style="7" customWidth="1"/>
+    <col min="6397" max="6397" width="113" style="7" customWidth="1"/>
+    <col min="6398" max="6651" width="8.88671875" style="7"/>
+    <col min="6652" max="6652" width="6.44140625" style="7" customWidth="1"/>
+    <col min="6653" max="6653" width="113" style="7" customWidth="1"/>
+    <col min="6654" max="6907" width="8.88671875" style="7"/>
+    <col min="6908" max="6908" width="6.44140625" style="7" customWidth="1"/>
+    <col min="6909" max="6909" width="113" style="7" customWidth="1"/>
+    <col min="6910" max="7163" width="8.88671875" style="7"/>
+    <col min="7164" max="7164" width="6.44140625" style="7" customWidth="1"/>
+    <col min="7165" max="7165" width="113" style="7" customWidth="1"/>
+    <col min="7166" max="7419" width="8.88671875" style="7"/>
+    <col min="7420" max="7420" width="6.44140625" style="7" customWidth="1"/>
+    <col min="7421" max="7421" width="113" style="7" customWidth="1"/>
+    <col min="7422" max="7675" width="8.88671875" style="7"/>
+    <col min="7676" max="7676" width="6.44140625" style="7" customWidth="1"/>
+    <col min="7677" max="7677" width="113" style="7" customWidth="1"/>
+    <col min="7678" max="7931" width="8.88671875" style="7"/>
+    <col min="7932" max="7932" width="6.44140625" style="7" customWidth="1"/>
+    <col min="7933" max="7933" width="113" style="7" customWidth="1"/>
+    <col min="7934" max="8187" width="8.88671875" style="7"/>
+    <col min="8188" max="8188" width="6.44140625" style="7" customWidth="1"/>
+    <col min="8189" max="8189" width="113" style="7" customWidth="1"/>
+    <col min="8190" max="8443" width="8.88671875" style="7"/>
+    <col min="8444" max="8444" width="6.44140625" style="7" customWidth="1"/>
+    <col min="8445" max="8445" width="113" style="7" customWidth="1"/>
+    <col min="8446" max="8699" width="8.88671875" style="7"/>
+    <col min="8700" max="8700" width="6.44140625" style="7" customWidth="1"/>
+    <col min="8701" max="8701" width="113" style="7" customWidth="1"/>
+    <col min="8702" max="8955" width="8.88671875" style="7"/>
+    <col min="8956" max="8956" width="6.44140625" style="7" customWidth="1"/>
+    <col min="8957" max="8957" width="113" style="7" customWidth="1"/>
+    <col min="8958" max="9211" width="8.88671875" style="7"/>
+    <col min="9212" max="9212" width="6.44140625" style="7" customWidth="1"/>
+    <col min="9213" max="9213" width="113" style="7" customWidth="1"/>
+    <col min="9214" max="9467" width="8.88671875" style="7"/>
+    <col min="9468" max="9468" width="6.44140625" style="7" customWidth="1"/>
+    <col min="9469" max="9469" width="113" style="7" customWidth="1"/>
+    <col min="9470" max="9723" width="8.88671875" style="7"/>
+    <col min="9724" max="9724" width="6.44140625" style="7" customWidth="1"/>
+    <col min="9725" max="9725" width="113" style="7" customWidth="1"/>
+    <col min="9726" max="9979" width="8.88671875" style="7"/>
+    <col min="9980" max="9980" width="6.44140625" style="7" customWidth="1"/>
+    <col min="9981" max="9981" width="113" style="7" customWidth="1"/>
+    <col min="9982" max="10235" width="8.88671875" style="7"/>
+    <col min="10236" max="10236" width="6.44140625" style="7" customWidth="1"/>
+    <col min="10237" max="10237" width="113" style="7" customWidth="1"/>
+    <col min="10238" max="10491" width="8.88671875" style="7"/>
+    <col min="10492" max="10492" width="6.44140625" style="7" customWidth="1"/>
+    <col min="10493" max="10493" width="113" style="7" customWidth="1"/>
+    <col min="10494" max="10747" width="8.88671875" style="7"/>
+    <col min="10748" max="10748" width="6.44140625" style="7" customWidth="1"/>
+    <col min="10749" max="10749" width="113" style="7" customWidth="1"/>
+    <col min="10750" max="11003" width="8.88671875" style="7"/>
+    <col min="11004" max="11004" width="6.44140625" style="7" customWidth="1"/>
+    <col min="11005" max="11005" width="113" style="7" customWidth="1"/>
+    <col min="11006" max="11259" width="8.88671875" style="7"/>
+    <col min="11260" max="11260" width="6.44140625" style="7" customWidth="1"/>
+    <col min="11261" max="11261" width="113" style="7" customWidth="1"/>
+    <col min="11262" max="11515" width="8.88671875" style="7"/>
+    <col min="11516" max="11516" width="6.44140625" style="7" customWidth="1"/>
+    <col min="11517" max="11517" width="113" style="7" customWidth="1"/>
+    <col min="11518" max="11771" width="8.88671875" style="7"/>
+    <col min="11772" max="11772" width="6.44140625" style="7" customWidth="1"/>
+    <col min="11773" max="11773" width="113" style="7" customWidth="1"/>
+    <col min="11774" max="12027" width="8.88671875" style="7"/>
+    <col min="12028" max="12028" width="6.44140625" style="7" customWidth="1"/>
+    <col min="12029" max="12029" width="113" style="7" customWidth="1"/>
+    <col min="12030" max="12283" width="8.88671875" style="7"/>
+    <col min="12284" max="12284" width="6.44140625" style="7" customWidth="1"/>
+    <col min="12285" max="12285" width="113" style="7" customWidth="1"/>
+    <col min="12286" max="12539" width="8.88671875" style="7"/>
+    <col min="12540" max="12540" width="6.44140625" style="7" customWidth="1"/>
+    <col min="12541" max="12541" width="113" style="7" customWidth="1"/>
+    <col min="12542" max="12795" width="8.88671875" style="7"/>
+    <col min="12796" max="12796" width="6.44140625" style="7" customWidth="1"/>
+    <col min="12797" max="12797" width="113" style="7" customWidth="1"/>
+    <col min="12798" max="13051" width="8.88671875" style="7"/>
+    <col min="13052" max="13052" width="6.44140625" style="7" customWidth="1"/>
+    <col min="13053" max="13053" width="113" style="7" customWidth="1"/>
+    <col min="13054" max="13307" width="8.88671875" style="7"/>
+    <col min="13308" max="13308" width="6.44140625" style="7" customWidth="1"/>
+    <col min="13309" max="13309" width="113" style="7" customWidth="1"/>
+    <col min="13310" max="13563" width="8.88671875" style="7"/>
+    <col min="13564" max="13564" width="6.44140625" style="7" customWidth="1"/>
+    <col min="13565" max="13565" width="113" style="7" customWidth="1"/>
+    <col min="13566" max="13819" width="8.88671875" style="7"/>
+    <col min="13820" max="13820" width="6.44140625" style="7" customWidth="1"/>
+    <col min="13821" max="13821" width="113" style="7" customWidth="1"/>
+    <col min="13822" max="14075" width="8.88671875" style="7"/>
+    <col min="14076" max="14076" width="6.44140625" style="7" customWidth="1"/>
+    <col min="14077" max="14077" width="113" style="7" customWidth="1"/>
+    <col min="14078" max="14331" width="8.88671875" style="7"/>
+    <col min="14332" max="14332" width="6.44140625" style="7" customWidth="1"/>
+    <col min="14333" max="14333" width="113" style="7" customWidth="1"/>
+    <col min="14334" max="14587" width="8.88671875" style="7"/>
+    <col min="14588" max="14588" width="6.44140625" style="7" customWidth="1"/>
+    <col min="14589" max="14589" width="113" style="7" customWidth="1"/>
+    <col min="14590" max="14843" width="8.88671875" style="7"/>
+    <col min="14844" max="14844" width="6.44140625" style="7" customWidth="1"/>
+    <col min="14845" max="14845" width="113" style="7" customWidth="1"/>
+    <col min="14846" max="15099" width="8.88671875" style="7"/>
+    <col min="15100" max="15100" width="6.44140625" style="7" customWidth="1"/>
+    <col min="15101" max="15101" width="113" style="7" customWidth="1"/>
+    <col min="15102" max="15355" width="8.88671875" style="7"/>
+    <col min="15356" max="15356" width="6.44140625" style="7" customWidth="1"/>
+    <col min="15357" max="15357" width="113" style="7" customWidth="1"/>
+    <col min="15358" max="15611" width="8.88671875" style="7"/>
+    <col min="15612" max="15612" width="6.44140625" style="7" customWidth="1"/>
+    <col min="15613" max="15613" width="113" style="7" customWidth="1"/>
+    <col min="15614" max="15867" width="8.88671875" style="7"/>
+    <col min="15868" max="15868" width="6.44140625" style="7" customWidth="1"/>
+    <col min="15869" max="15869" width="113" style="7" customWidth="1"/>
+    <col min="15870" max="16123" width="8.88671875" style="7"/>
+    <col min="16124" max="16124" width="6.44140625" style="7" customWidth="1"/>
+    <col min="16125" max="16125" width="113" style="7" customWidth="1"/>
+    <col min="16126" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="8">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27.6">
-      <c r="A6" s="8">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="8">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="8">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="41.4">
-      <c r="A10" s="8">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="8">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="8"/>
+      <c r="B11" s="7"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="8">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="8"/>
+      <c r="B12" s="7"/>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="8">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="8">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="8">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="8">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="15"/>
+      <c r="B17" s="14"/>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="16"/>
-      <c r="B18" s="9" t="s">
+      <c r="A18" s="15"/>
+      <c r="B18" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="9" t="s">
+      <c r="A19" s="16"/>
+      <c r="B19" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1151,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18.44140625" style="1" customWidth="1"/>
@@ -1210,16 +1368,16 @@
       <c r="X1" s="6"/>
     </row>
     <row r="2" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C2" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="19">
         <v>200</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -1230,16 +1388,16 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="C3" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="19">
         <v>100</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -1250,17 +1408,59 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="12.75" customHeight="1">
+      <c r="A5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="2">
-        <v>1000</v>
+      <c r="B5" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="19">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="12.75" customHeight="1">
+      <c r="A6" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="19">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="12.75" customHeight="1">
+      <c r="A7" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="19">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
